--- a/artfynd/A 36346-2026 artfynd.xlsx
+++ b/artfynd/A 36346-2026 artfynd.xlsx
@@ -2257,7 +2257,7 @@
         <v>136307448</v>
       </c>
       <c r="B15" t="n">
-        <v>57807</v>
+        <v>57809</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>136307363</v>
       </c>
       <c r="B17" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>136307358</v>
       </c>
       <c r="B18" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
